--- a/campanhas/neoprene/kw-planner/kw-neoprene.xlsx
+++ b/campanhas/neoprene/kw-planner/kw-neoprene.xlsx
@@ -24,7 +24,7 @@
     <sheet name="fora-da-campanha" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Consolidado'!$A$1:$H$337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Consolidado'!$A$1:$H$324</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'sapatilha-aquatica'!$A$1:$H$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'sapatilha-neoprene'!$A$1:$H$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'sapatilha-areia'!$A$1:$H$6</definedName>
@@ -35,9 +35,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'surf-vestuario'!$A$1:$H$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'natacao-vestuario'!$A$1:$H$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'categoria'!$A$1:$H$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'marca'!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'marca'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'concorrencia'!$A$1:$H$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'fora-da-campanha'!$A$1:$H$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'fora-da-campanha'!$A$1:$H$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>30940</v>
+        <v>28530</v>
       </c>
     </row>
     <row r="18">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>106780</v>
+        <v>104300</v>
       </c>
     </row>
     <row r="20">
@@ -3072,7 +3072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3130,7 +3130,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>use zero hora</t>
+          <t>bermuda use zero hora</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -3138,11 +3138,15 @@
           <t>neoprene-marca</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" s="11" t="n">
-        <v>0</v>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>n/c</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>n/c</t>
+        </is>
       </c>
       <c r="E2" s="9" t="inlineStr"/>
       <c r="F2" s="9" t="inlineStr">
@@ -3160,7 +3164,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>zero hora surf</t>
+          <t>camiseta neoprene use zero hora</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -3168,11 +3172,15 @@
           <t>neoprene-marca</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" s="12" t="n">
-        <v>0</v>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>n/c</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>n/c</t>
+        </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
@@ -3190,7 +3198,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>usezerohora</t>
+          <t>sapatilha use zero hora</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -3198,11 +3206,15 @@
           <t>neoprene-marca</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>0</v>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>n/c</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>n/c</t>
+        </is>
       </c>
       <c r="E4" s="9" t="inlineStr"/>
       <c r="F4" s="9" t="inlineStr">
@@ -3220,7 +3232,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>bermuda use zero hora</t>
+          <t>use zero hora neoprene</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -3251,110 +3263,8 @@
       </c>
       <c r="H5" s="4" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>camiseta neoprene use zero hora</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>neoprene-marca</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>n/c</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>n/c</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>Phrase</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>sapatilha use zero hora</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>neoprene-marca</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>n/c</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>n/c</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Phrase</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>use zero hora neoprene</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>neoprene-marca</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>n/c</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>n/c</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>Phrase</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:H5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3704,7 +3614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3952,7 +3862,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>roupa de natação infantil</t>
+          <t>roupa para mergulho</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -3968,7 +3878,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -3983,14 +3893,14 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>negativa confirmada: linha adulta</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>roupa para mergulho</t>
+          <t>roupa de borracha</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -3999,7 +3909,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>720</v>
+        <v>590</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>0</v>
@@ -4021,14 +3931,14 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>roupa de borracha</t>
+          <t>roupas de mergulho masculino</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -4059,14 +3969,14 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>roupas de mergulho masculino</t>
+          <t>traje de mergulho</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -4082,7 +3992,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -4104,7 +4014,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>traje de mergulho</t>
+          <t>long john masculino</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -4113,14 +4023,14 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>590</v>
+        <v>480</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -4135,14 +4045,14 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>long john masculino</t>
+          <t>loja de natação perto de mim</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -4151,14 +4061,14 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>480</v>
+        <v>390</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -4173,14 +4083,14 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>intencao de loja fisica/generica</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>loja de natação perto de mim</t>
+          <t>roupa de borracha para triathlon</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -4196,7 +4106,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational, Transactional</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -4211,14 +4121,14 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>intencao de loja fisica/generica</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>roupa de borracha para triathlon</t>
+          <t>john surf</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -4227,14 +4137,14 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Informational, Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -4249,14 +4159,14 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>acessorios natação</t>
+          <t>loja de natacao</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -4287,14 +4197,14 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>intencao de loja fisica/generica</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>acessorios para natação</t>
+          <t>macacao para natacao feminina</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -4310,7 +4220,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -4325,14 +4235,14 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>john surf</t>
+          <t>macacão de natação feminino</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -4348,7 +4258,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -4370,7 +4280,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>loja de natacao</t>
+          <t>roupa de mergulho profissional</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -4386,7 +4296,7 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -4401,14 +4311,14 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>intencao de loja fisica/generica</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>macacao para natacao feminina</t>
+          <t>roupa de nadador</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -4424,7 +4334,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -4439,14 +4349,14 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>macacão de natação feminino</t>
+          <t>equipamentos da natação</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -4455,7 +4365,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>0</v>
@@ -4477,14 +4387,14 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>roupa de mergulho profissional</t>
+          <t>equipamentos para natação</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -4493,7 +4403,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>0</v>
@@ -4515,14 +4425,14 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>roupa de nadador</t>
+          <t>loja de natação</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -4531,14 +4441,14 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -4553,14 +4463,14 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>intencao de loja fisica/generica</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>equipamentos da natação</t>
+          <t>macacao natacao</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -4576,7 +4486,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Transactional</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -4591,14 +4501,14 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>equipamentos para natação</t>
+          <t>maios esportivos</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -4614,7 +4524,7 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
@@ -4629,14 +4539,14 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>loja de natação</t>
+          <t>traje arena feminino</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -4652,7 +4562,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -4667,14 +4577,14 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>intencao de loja fisica/generica</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>macacao natacao</t>
+          <t>traje de natação masculino</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -4690,7 +4600,7 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Informational, Transactional</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
@@ -4705,14 +4615,14 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>maios esportivos</t>
+          <t>macacao neoprene</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -4721,14 +4631,14 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -4743,14 +4653,14 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>roupa para natação infantil</t>
+          <t>maio masculino natação</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -4759,7 +4669,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>0</v>
@@ -4781,14 +4691,14 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>negativa confirmada: linha adulta</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>traje arena feminino</t>
+          <t>maiô masculino para natação</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -4797,14 +4707,14 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -4826,7 +4736,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>traje de natação masculino</t>
+          <t>maiô natação masculino</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -4835,14 +4745,14 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -4864,7 +4774,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>macacao neoprene</t>
+          <t>surf feminino</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -4880,7 +4790,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -4895,14 +4805,14 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>maio masculino natação</t>
+          <t>traje de natacao</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -4918,7 +4828,7 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Transactional</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
@@ -4940,7 +4850,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>maiô masculino para natação</t>
+          <t>traje de natação</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -4978,7 +4888,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>maiô natação masculino</t>
+          <t>traje natação feminino</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -4994,7 +4904,7 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
@@ -5016,7 +4926,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>surf feminino</t>
+          <t>calção de natação</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -5025,14 +4935,14 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="D35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Informational, Transactional</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -5047,14 +4957,14 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>traje de natacao</t>
+          <t>macacão de mergulho</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -5063,14 +4973,14 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Informational, Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
@@ -5085,14 +4995,14 @@
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>traje de natação</t>
+          <t>material de natacao</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -5101,14 +5011,14 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="D37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -5123,14 +5033,14 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>traje natação feminino</t>
+          <t>material para natação</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -5139,14 +5049,14 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
@@ -5161,14 +5071,14 @@
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>acessorios para natacao</t>
+          <t>natação materiais</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -5184,7 +5094,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -5199,14 +5109,14 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>calção de natação</t>
+          <t>artigos de natação</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -5215,14 +5125,14 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Informational, Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -5237,14 +5147,14 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>macacão de mergulho</t>
+          <t>artigos para natação</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -5253,7 +5163,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D41" s="12" t="n">
         <v>0</v>
@@ -5275,14 +5185,14 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>material de natacao</t>
+          <t>calcao natacao</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -5291,7 +5201,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>0</v>
@@ -5313,14 +5223,14 @@
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>material para natação</t>
+          <t>equipamentos para natacao</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -5329,14 +5239,14 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -5358,7 +5268,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>natação materiais</t>
+          <t>long surf</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -5367,7 +5277,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>0</v>
@@ -5396,7 +5306,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>roupa de natação infantil masculino</t>
+          <t>macacao para natacao</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -5405,7 +5315,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D45" s="12" t="n">
         <v>0</v>
@@ -5427,14 +5337,14 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>negativa confirmada: linha adulta</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>acessórios natação</t>
+          <t>macacão de natação masculino</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -5450,7 +5360,7 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
@@ -5465,14 +5375,14 @@
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>artigos de natação</t>
+          <t>macacão neoprene</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -5488,7 +5398,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -5503,14 +5413,14 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>artigos para natação</t>
+          <t>marcas de roupa de surf</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -5541,14 +5451,14 @@
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>pesquisa de marca/moda generica</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>calcao natacao</t>
+          <t>marcas de surfista</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -5579,14 +5489,14 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>pesquisa de marca/moda generica</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>equipamentos para natacao</t>
+          <t>roupa de nadar</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -5602,7 +5512,7 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
@@ -5617,14 +5527,14 @@
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>long surf</t>
+          <t>roupa mergulho neoprene</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -5640,7 +5550,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -5655,14 +5565,14 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>macacao para natacao</t>
+          <t>surf suit</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -5678,7 +5588,7 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
@@ -5700,7 +5610,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>macacão de natação masculino</t>
+          <t>traje para natação</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -5731,14 +5641,14 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>macacão neoprene</t>
+          <t>calção de natação masculino</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
@@ -5747,14 +5657,14 @@
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
@@ -5769,14 +5679,14 @@
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>marcas de roupa de surf</t>
+          <t>calção para natação</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -5785,14 +5695,14 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Transactional</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -5807,14 +5717,14 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>pesquisa de marca/moda generica</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>marcas de surfista</t>
+          <t>loja roupa de surf</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -5823,7 +5733,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>0</v>
@@ -5845,14 +5755,14 @@
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>pesquisa de marca/moda generica</t>
+          <t>intencao de loja fisica/generica</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>roupa de nadar</t>
+          <t>macacao surf feminino</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -5861,14 +5771,14 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -5883,14 +5793,14 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>roupa mergulho neoprene</t>
+          <t>macacão de surf feminino</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -5899,14 +5809,14 @@
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
@@ -5921,14 +5831,14 @@
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>surf suit</t>
+          <t>roupa de borracha feminina</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -5937,7 +5847,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D59" s="12" t="n">
         <v>0</v>
@@ -5959,14 +5869,14 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>traje para natação</t>
+          <t>roupa para mergulho neoprene</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -5975,14 +5885,14 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
@@ -5997,14 +5907,14 @@
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>acessórios para natação</t>
+          <t>roupa para nadar</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -6020,7 +5930,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -6035,14 +5945,14 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>calção de natação masculino</t>
+          <t>roupas de mergulho 5mm</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -6058,7 +5968,7 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
@@ -6073,14 +5983,14 @@
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>calção para natação</t>
+          <t>surf long john</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -6096,7 +6006,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Informational, Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -6111,14 +6021,14 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>loja roupa de surf</t>
+          <t>surf neoprene suit</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -6149,14 +6059,14 @@
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>intencao de loja fisica/generica</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>macacao surf feminino</t>
+          <t>calça de natação</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -6165,7 +6075,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D65" s="12" t="n">
         <v>0</v>
@@ -6177,7 +6087,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -6187,14 +6097,14 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>macacão de surf feminino</t>
+          <t>calça para natação</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -6203,19 +6113,19 @@
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr">
@@ -6225,14 +6135,14 @@
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>roupa de borracha feminina</t>
+          <t>loja de roupa de natação</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -6241,7 +6151,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D67" s="12" t="n">
         <v>0</v>
@@ -6253,7 +6163,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -6263,14 +6173,14 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>intencao de loja fisica/generica</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>roupa de natação feminina infantil</t>
+          <t>macacao neoprene feminino</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -6279,19 +6189,19 @@
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
@@ -6301,14 +6211,14 @@
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>negativa confirmada: linha adulta</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>roupa para mergulho neoprene</t>
+          <t>macacão neoprene feminino</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6317,7 +6227,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D69" s="12" t="n">
         <v>0</v>
@@ -6329,7 +6239,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -6339,14 +6249,14 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>roupa para nadar</t>
+          <t>material para natacao</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -6355,19 +6265,19 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
@@ -6377,14 +6287,14 @@
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>roupas de mergulho 5mm</t>
+          <t>melhores maios para natação</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -6393,19 +6303,19 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -6415,14 +6325,14 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>surf long john</t>
+          <t>moda surf masculina</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -6431,7 +6341,7 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D72" s="11" t="n">
         <v>0</v>
@@ -6443,7 +6353,7 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G72" s="9" t="inlineStr">
@@ -6453,14 +6363,14 @@
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>pesquisa de marca/moda generica</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>surf neoprene suit</t>
+          <t>natação masculina</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6469,19 +6379,19 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -6491,14 +6401,14 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>acessorios natacao</t>
+          <t>roupa de surf john</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -6529,14 +6439,14 @@
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>calça de natação</t>
+          <t>roupa de natação masculina profissional</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -6545,16 +6455,12 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Informational, Commercial</t>
-        </is>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>Exact</t>
@@ -6567,14 +6473,14 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>calça para natação</t>
+          <t>roupa para aula de natação masculino</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -6583,16 +6489,12 @@
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E76" s="9" t="inlineStr"/>
       <c r="F76" s="9" t="inlineStr">
         <is>
           <t>Exact</t>
@@ -6605,384 +6507,12 @@
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>loja de roupa de natação</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>intencao de loja fisica/generica</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="9" t="inlineStr">
-        <is>
-          <t>macacao neoprene feminino</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="D78" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>produto nao vendido (roupa fechada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>macacão neoprene feminino</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Informational, Commercial</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>produto nao vendido (roupa fechada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
-        <is>
-          <t>material para natacao</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="D80" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>Informational, Commercial</t>
-        </is>
-      </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>melhores maios para natação</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>peca de natacao que nao vendemos</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>moda surf masculina</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="D82" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>pesquisa de marca/moda generica</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>natação masculina</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
           <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>roupa de surf john</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C84" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="D84" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>produto nao vendido (roupa fechada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>roupa de natação masculina profissional</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D85" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>aderencia baixa ao produto</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>roupa para aula de natação masculino</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C86" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="D86" s="11" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E86" s="9" t="inlineStr"/>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G86" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>aderencia baixa ao produto</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H86"/>
+  <autoFilter ref="A1:H76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6993,7 +6523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H337"/>
+  <dimension ref="A1:H324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -14811,7 +14341,7 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>use zero hora</t>
+          <t>bermuda use zero hora</t>
         </is>
       </c>
       <c r="B238" s="9" t="inlineStr">
@@ -14819,11 +14349,15 @@
           <t>neoprene-marca</t>
         </is>
       </c>
-      <c r="C238" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D238" s="11" t="n">
-        <v>0</v>
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>n/c</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="inlineStr">
+        <is>
+          <t>n/c</t>
+        </is>
       </c>
       <c r="E238" s="9" t="inlineStr"/>
       <c r="F238" s="9" t="inlineStr">
@@ -14841,7 +14375,7 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>zero hora surf</t>
+          <t>camiseta neoprene use zero hora</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
@@ -14849,11 +14383,15 @@
           <t>neoprene-marca</t>
         </is>
       </c>
-      <c r="C239" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D239" s="12" t="n">
-        <v>0</v>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>n/c</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="inlineStr">
+        <is>
+          <t>n/c</t>
+        </is>
       </c>
       <c r="E239" s="4" t="inlineStr"/>
       <c r="F239" s="4" t="inlineStr">
@@ -14871,7 +14409,7 @@
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>usezerohora</t>
+          <t>sapatilha use zero hora</t>
         </is>
       </c>
       <c r="B240" s="9" t="inlineStr">
@@ -14879,11 +14417,15 @@
           <t>neoprene-marca</t>
         </is>
       </c>
-      <c r="C240" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D240" s="11" t="n">
-        <v>0</v>
+      <c r="C240" s="9" t="inlineStr">
+        <is>
+          <t>n/c</t>
+        </is>
+      </c>
+      <c r="D240" s="9" t="inlineStr">
+        <is>
+          <t>n/c</t>
+        </is>
       </c>
       <c r="E240" s="9" t="inlineStr"/>
       <c r="F240" s="9" t="inlineStr">
@@ -14901,7 +14443,7 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>bermuda use zero hora</t>
+          <t>use zero hora neoprene</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -14935,12 +14477,12 @@
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>camiseta neoprene use zero hora</t>
+          <t>camisa de neoprene mormaii</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
         <is>
-          <t>neoprene-marca</t>
+          <t>neoprene-concorrencia (nao ativar)</t>
         </is>
       </c>
       <c r="C242" s="9" t="inlineStr">
@@ -14956,12 +14498,12 @@
       <c r="E242" s="9" t="inlineStr"/>
       <c r="F242" s="9" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G242" s="9" t="inlineStr">
         <is>
-          <t>kw-manager</t>
+          <t>lista-colada</t>
         </is>
       </c>
       <c r="H242" s="9" t="inlineStr"/>
@@ -14969,12 +14511,12 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>sapatilha use zero hora</t>
+          <t>camisa mergulho mormaii manga longa neolycra</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>neoprene-marca</t>
+          <t>neoprene-concorrencia (nao ativar)</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
@@ -14990,12 +14532,12 @@
       <c r="E243" s="4" t="inlineStr"/>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G243" s="4" t="inlineStr">
         <is>
-          <t>kw-manager</t>
+          <t>lista-colada</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -15003,12 +14545,12 @@
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
         <is>
-          <t>use zero hora neoprene</t>
+          <t>camisa mormaii neoprene</t>
         </is>
       </c>
       <c r="B244" s="9" t="inlineStr">
         <is>
-          <t>neoprene-marca</t>
+          <t>neoprene-concorrencia (nao ativar)</t>
         </is>
       </c>
       <c r="C244" s="9" t="inlineStr">
@@ -15024,12 +14566,12 @@
       <c r="E244" s="9" t="inlineStr"/>
       <c r="F244" s="9" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G244" s="9" t="inlineStr">
         <is>
-          <t>kw-manager</t>
+          <t>lista-colada</t>
         </is>
       </c>
       <c r="H244" s="9" t="inlineStr"/>
@@ -15037,7 +14579,7 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>camisa de neoprene mormaii</t>
+          <t>camisa neoprene billabong</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
@@ -15071,7 +14613,7 @@
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
         <is>
-          <t>camisa mergulho mormaii manga longa neolycra</t>
+          <t>camisa neoprene decathlon</t>
         </is>
       </c>
       <c r="B246" s="9" t="inlineStr">
@@ -15105,7 +14647,7 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>camisa mormaii neoprene</t>
+          <t>camisa neoprene hurley</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -15139,7 +14681,7 @@
     <row r="248">
       <c r="A248" s="9" t="inlineStr">
         <is>
-          <t>camisa neoprene billabong</t>
+          <t>camisa neoprene mormaii</t>
         </is>
       </c>
       <c r="B248" s="9" t="inlineStr">
@@ -15173,7 +14715,7 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>camisa neoprene decathlon</t>
+          <t>camisa neoprene rip curl</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
@@ -15207,109 +14749,121 @@
     <row r="250">
       <c r="A250" s="9" t="inlineStr">
         <is>
-          <t>camisa neoprene hurley</t>
+          <t>roupa de mergulho</t>
         </is>
       </c>
       <c r="B250" s="9" t="inlineStr">
         <is>
-          <t>neoprene-concorrencia (nao ativar)</t>
-        </is>
-      </c>
-      <c r="C250" s="9" t="inlineStr">
-        <is>
-          <t>n/c</t>
-        </is>
-      </c>
-      <c r="D250" s="9" t="inlineStr">
-        <is>
-          <t>n/c</t>
-        </is>
-      </c>
-      <c r="E250" s="9" t="inlineStr"/>
+          <t>fora-da-campanha (observacao)</t>
+        </is>
+      </c>
+      <c r="C250" s="10" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D250" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" s="9" t="inlineStr">
+        <is>
+          <t>Informational, Commercial</t>
+        </is>
+      </c>
       <c r="F250" s="9" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Phrase</t>
         </is>
       </c>
       <c r="G250" s="9" t="inlineStr">
         <is>
-          <t>lista-colada</t>
-        </is>
-      </c>
-      <c r="H250" s="9" t="inlineStr"/>
+          <t>kw-manager</t>
+        </is>
+      </c>
+      <c r="H250" s="9" t="inlineStr">
+        <is>
+          <t>intencao mergulho: produto nao atende</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>camisa neoprene mormaii</t>
+          <t>long john</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>neoprene-concorrencia (nao ativar)</t>
-        </is>
-      </c>
-      <c r="C251" s="4" t="inlineStr">
-        <is>
-          <t>n/c</t>
-        </is>
-      </c>
-      <c r="D251" s="4" t="inlineStr">
-        <is>
-          <t>n/c</t>
-        </is>
-      </c>
-      <c r="E251" s="4" t="inlineStr"/>
+          <t>fora-da-campanha (observacao)</t>
+        </is>
+      </c>
+      <c r="C251" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D251" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" s="4" t="inlineStr">
+        <is>
+          <t>Informational, Commercial</t>
+        </is>
+      </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Phrase</t>
         </is>
       </c>
       <c r="G251" s="4" t="inlineStr">
         <is>
-          <t>lista-colada</t>
-        </is>
-      </c>
-      <c r="H251" s="4" t="inlineStr"/>
+          <t>kw-manager</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="inlineStr">
+        <is>
+          <t>produto nao vendido (roupa fechada)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>camisa neoprene rip curl</t>
+          <t>wetsuit wet</t>
         </is>
       </c>
       <c r="B252" s="9" t="inlineStr">
         <is>
-          <t>neoprene-concorrencia (nao ativar)</t>
-        </is>
-      </c>
-      <c r="C252" s="9" t="inlineStr">
-        <is>
-          <t>n/c</t>
-        </is>
-      </c>
-      <c r="D252" s="9" t="inlineStr">
-        <is>
-          <t>n/c</t>
-        </is>
-      </c>
-      <c r="E252" s="9" t="inlineStr"/>
+          <t>fora-da-campanha (observacao)</t>
+        </is>
+      </c>
+      <c r="C252" s="10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D252" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" s="9" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
       <c r="F252" s="9" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Phrase</t>
         </is>
       </c>
       <c r="G252" s="9" t="inlineStr">
         <is>
-          <t>lista-colada</t>
-        </is>
-      </c>
-      <c r="H252" s="9" t="inlineStr"/>
+          <t>kw-manager</t>
+        </is>
+      </c>
+      <c r="H252" s="9" t="inlineStr">
+        <is>
+          <t>produto nao vendido (roupa fechada)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>roupa de mergulho</t>
+          <t>long john john</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
@@ -15318,14 +14872,14 @@
         </is>
       </c>
       <c r="C253" s="5" t="n">
-        <v>8100</v>
+        <v>1300</v>
       </c>
       <c r="D253" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
@@ -15340,14 +14894,14 @@
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>long john</t>
+          <t>roupas de mergulho feminina</t>
         </is>
       </c>
       <c r="B254" s="9" t="inlineStr">
@@ -15356,14 +14910,14 @@
         </is>
       </c>
       <c r="C254" s="10" t="n">
-        <v>2400</v>
+        <v>1000</v>
       </c>
       <c r="D254" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F254" s="9" t="inlineStr">
@@ -15378,14 +14932,14 @@
       </c>
       <c r="H254" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>wetsuit wet</t>
+          <t>roupa para mergulho</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
@@ -15394,14 +14948,14 @@
         </is>
       </c>
       <c r="C255" s="5" t="n">
-        <v>1600</v>
+        <v>720</v>
       </c>
       <c r="D255" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
@@ -15416,14 +14970,14 @@
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>long john john</t>
+          <t>roupa de borracha</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
@@ -15432,14 +14986,14 @@
         </is>
       </c>
       <c r="C256" s="10" t="n">
-        <v>1300</v>
+        <v>590</v>
       </c>
       <c r="D256" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
@@ -15454,14 +15008,14 @@
       </c>
       <c r="H256" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>roupas de mergulho feminina</t>
+          <t>roupas de mergulho masculino</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -15470,14 +15024,14 @@
         </is>
       </c>
       <c r="C257" s="5" t="n">
-        <v>1000</v>
+        <v>590</v>
       </c>
       <c r="D257" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
@@ -15499,7 +15053,7 @@
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>roupa de natação infantil</t>
+          <t>traje de mergulho</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr">
@@ -15508,7 +15062,7 @@
         </is>
       </c>
       <c r="C258" s="10" t="n">
-        <v>720</v>
+        <v>590</v>
       </c>
       <c r="D258" s="11" t="n">
         <v>0</v>
@@ -15530,14 +15084,14 @@
       </c>
       <c r="H258" s="9" t="inlineStr">
         <is>
-          <t>negativa confirmada: linha adulta</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>roupa para mergulho</t>
+          <t>long john masculino</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
@@ -15546,14 +15100,14 @@
         </is>
       </c>
       <c r="C259" s="5" t="n">
-        <v>720</v>
+        <v>480</v>
       </c>
       <c r="D259" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
@@ -15568,14 +15122,14 @@
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>roupa de borracha</t>
+          <t>loja de natação perto de mim</t>
         </is>
       </c>
       <c r="B260" s="9" t="inlineStr">
@@ -15584,14 +15138,14 @@
         </is>
       </c>
       <c r="C260" s="10" t="n">
-        <v>590</v>
+        <v>390</v>
       </c>
       <c r="D260" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
@@ -15606,14 +15160,14 @@
       </c>
       <c r="H260" s="9" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>intencao de loja fisica/generica</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>roupas de mergulho masculino</t>
+          <t>roupa de borracha para triathlon</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -15622,14 +15176,14 @@
         </is>
       </c>
       <c r="C261" s="5" t="n">
-        <v>590</v>
+        <v>390</v>
       </c>
       <c r="D261" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Informational, Transactional</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
@@ -15644,14 +15198,14 @@
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>traje de mergulho</t>
+          <t>john surf</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr">
@@ -15660,14 +15214,14 @@
         </is>
       </c>
       <c r="C262" s="10" t="n">
-        <v>590</v>
+        <v>320</v>
       </c>
       <c r="D262" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
@@ -15682,14 +15236,14 @@
       </c>
       <c r="H262" s="9" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>long john masculino</t>
+          <t>loja de natacao</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -15698,7 +15252,7 @@
         </is>
       </c>
       <c r="C263" s="5" t="n">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="D263" s="12" t="n">
         <v>0</v>
@@ -15720,14 +15274,14 @@
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>intencao de loja fisica/generica</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>loja de natação perto de mim</t>
+          <t>macacao para natacao feminina</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
@@ -15736,14 +15290,14 @@
         </is>
       </c>
       <c r="C264" s="10" t="n">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="D264" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
@@ -15758,14 +15312,14 @@
       </c>
       <c r="H264" s="9" t="inlineStr">
         <is>
-          <t>intencao de loja fisica/generica</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>roupa de borracha para triathlon</t>
+          <t>macacão de natação feminino</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
@@ -15774,14 +15328,14 @@
         </is>
       </c>
       <c r="C265" s="5" t="n">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="D265" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>Informational, Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
@@ -15796,14 +15350,14 @@
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>acessorios natação</t>
+          <t>roupa de mergulho profissional</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
@@ -15819,7 +15373,7 @@
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
@@ -15834,14 +15388,14 @@
       </c>
       <c r="H266" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>acessorios para natação</t>
+          <t>roupa de nadador</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
@@ -15857,7 +15411,7 @@
       </c>
       <c r="E267" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
@@ -15872,14 +15426,14 @@
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>john surf</t>
+          <t>equipamentos da natação</t>
         </is>
       </c>
       <c r="B268" s="9" t="inlineStr">
@@ -15888,14 +15442,14 @@
         </is>
       </c>
       <c r="C268" s="10" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="D268" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
@@ -15910,14 +15464,14 @@
       </c>
       <c r="H268" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>loja de natacao</t>
+          <t>equipamentos para natação</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
@@ -15926,14 +15480,14 @@
         </is>
       </c>
       <c r="C269" s="5" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="D269" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E269" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
@@ -15948,14 +15502,14 @@
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
-          <t>intencao de loja fisica/generica</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>macacao para natacao feminina</t>
+          <t>loja de natação</t>
         </is>
       </c>
       <c r="B270" s="9" t="inlineStr">
@@ -15964,14 +15518,14 @@
         </is>
       </c>
       <c r="C270" s="10" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="D270" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
@@ -15986,14 +15540,14 @@
       </c>
       <c r="H270" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>intencao de loja fisica/generica</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>macacão de natação feminino</t>
+          <t>macacao natacao</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -16002,14 +15556,14 @@
         </is>
       </c>
       <c r="C271" s="5" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="D271" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Transactional</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
@@ -16031,7 +15585,7 @@
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>roupa de mergulho profissional</t>
+          <t>maios esportivos</t>
         </is>
       </c>
       <c r="B272" s="9" t="inlineStr">
@@ -16040,14 +15594,14 @@
         </is>
       </c>
       <c r="C272" s="10" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="D272" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
@@ -16062,14 +15616,14 @@
       </c>
       <c r="H272" s="9" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>roupa de nadador</t>
+          <t>traje arena feminino</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
@@ -16078,7 +15632,7 @@
         </is>
       </c>
       <c r="C273" s="5" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="D273" s="12" t="n">
         <v>0</v>
@@ -16100,14 +15654,14 @@
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>equipamentos da natação</t>
+          <t>traje de natação masculino</t>
         </is>
       </c>
       <c r="B274" s="9" t="inlineStr">
@@ -16123,7 +15677,7 @@
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
@@ -16138,14 +15692,14 @@
       </c>
       <c r="H274" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>equipamentos para natação</t>
+          <t>macacao neoprene</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -16154,14 +15708,14 @@
         </is>
       </c>
       <c r="C275" s="5" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D275" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
@@ -16176,14 +15730,14 @@
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>loja de natação</t>
+          <t>maio masculino natação</t>
         </is>
       </c>
       <c r="B276" s="9" t="inlineStr">
@@ -16192,14 +15746,14 @@
         </is>
       </c>
       <c r="C276" s="10" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D276" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
@@ -16214,14 +15768,14 @@
       </c>
       <c r="H276" s="9" t="inlineStr">
         <is>
-          <t>intencao de loja fisica/generica</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>macacao natacao</t>
+          <t>maiô masculino para natação</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
@@ -16230,14 +15784,14 @@
         </is>
       </c>
       <c r="C277" s="5" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D277" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>Informational, Transactional</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
@@ -16252,14 +15806,14 @@
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>maios esportivos</t>
+          <t>maiô natação masculino</t>
         </is>
       </c>
       <c r="B278" s="9" t="inlineStr">
@@ -16268,14 +15822,14 @@
         </is>
       </c>
       <c r="C278" s="10" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D278" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
@@ -16297,7 +15851,7 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>roupa para natação infantil</t>
+          <t>surf feminino</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
@@ -16306,14 +15860,14 @@
         </is>
       </c>
       <c r="C279" s="5" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D279" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E279" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
@@ -16328,14 +15882,14 @@
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
-          <t>negativa confirmada: linha adulta</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>traje arena feminino</t>
+          <t>traje de natacao</t>
         </is>
       </c>
       <c r="B280" s="9" t="inlineStr">
@@ -16344,14 +15898,14 @@
         </is>
       </c>
       <c r="C280" s="10" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D280" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Transactional</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
@@ -16373,7 +15927,7 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>traje de natação masculino</t>
+          <t>traje de natação</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -16382,7 +15936,7 @@
         </is>
       </c>
       <c r="C281" s="5" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="D281" s="12" t="n">
         <v>0</v>
@@ -16411,7 +15965,7 @@
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>macacao neoprene</t>
+          <t>traje natação feminino</t>
         </is>
       </c>
       <c r="B282" s="9" t="inlineStr">
@@ -16427,7 +15981,7 @@
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
@@ -16442,14 +15996,14 @@
       </c>
       <c r="H282" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>maio masculino natação</t>
+          <t>calção de natação</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -16458,14 +16012,14 @@
         </is>
       </c>
       <c r="C283" s="5" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="D283" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E283" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Transactional</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
@@ -16487,7 +16041,7 @@
     <row r="284">
       <c r="A284" s="9" t="inlineStr">
         <is>
-          <t>maiô masculino para natação</t>
+          <t>macacão de mergulho</t>
         </is>
       </c>
       <c r="B284" s="9" t="inlineStr">
@@ -16496,14 +16050,14 @@
         </is>
       </c>
       <c r="C284" s="10" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="D284" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
@@ -16518,14 +16072,14 @@
       </c>
       <c r="H284" s="9" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>maiô natação masculino</t>
+          <t>material de natacao</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -16534,14 +16088,14 @@
         </is>
       </c>
       <c r="C285" s="5" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="D285" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E285" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
@@ -16556,14 +16110,14 @@
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="9" t="inlineStr">
         <is>
-          <t>surf feminino</t>
+          <t>material para natação</t>
         </is>
       </c>
       <c r="B286" s="9" t="inlineStr">
@@ -16572,14 +16126,14 @@
         </is>
       </c>
       <c r="C286" s="10" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="D286" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
@@ -16594,14 +16148,14 @@
       </c>
       <c r="H286" s="9" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>traje de natacao</t>
+          <t>natação materiais</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -16610,14 +16164,14 @@
         </is>
       </c>
       <c r="C287" s="5" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="D287" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E287" s="4" t="inlineStr">
         <is>
-          <t>Informational, Transactional</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
@@ -16632,14 +16186,14 @@
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="9" t="inlineStr">
         <is>
-          <t>traje de natação</t>
+          <t>artigos de natação</t>
         </is>
       </c>
       <c r="B288" s="9" t="inlineStr">
@@ -16648,14 +16202,14 @@
         </is>
       </c>
       <c r="C288" s="10" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="D288" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
@@ -16670,14 +16224,14 @@
       </c>
       <c r="H288" s="9" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>traje natação feminino</t>
+          <t>artigos para natação</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
@@ -16686,14 +16240,14 @@
         </is>
       </c>
       <c r="C289" s="5" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="D289" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
@@ -16708,14 +16262,14 @@
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="9" t="inlineStr">
         <is>
-          <t>acessorios para natacao</t>
+          <t>calcao natacao</t>
         </is>
       </c>
       <c r="B290" s="9" t="inlineStr">
@@ -16724,7 +16278,7 @@
         </is>
       </c>
       <c r="C290" s="10" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D290" s="11" t="n">
         <v>0</v>
@@ -16746,14 +16300,14 @@
       </c>
       <c r="H290" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>calção de natação</t>
+          <t>equipamentos para natacao</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -16762,14 +16316,14 @@
         </is>
       </c>
       <c r="C291" s="5" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D291" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E291" s="4" t="inlineStr">
         <is>
-          <t>Informational, Transactional</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
@@ -16784,14 +16338,14 @@
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="9" t="inlineStr">
         <is>
-          <t>macacão de mergulho</t>
+          <t>long surf</t>
         </is>
       </c>
       <c r="B292" s="9" t="inlineStr">
@@ -16800,14 +16354,14 @@
         </is>
       </c>
       <c r="C292" s="10" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D292" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
@@ -16822,14 +16376,14 @@
       </c>
       <c r="H292" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>material de natacao</t>
+          <t>macacao para natacao</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -16838,14 +16392,14 @@
         </is>
       </c>
       <c r="C293" s="5" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D293" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E293" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
@@ -16860,14 +16414,14 @@
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="9" t="inlineStr">
         <is>
-          <t>material para natação</t>
+          <t>macacão de natação masculino</t>
         </is>
       </c>
       <c r="B294" s="9" t="inlineStr">
@@ -16876,14 +16430,14 @@
         </is>
       </c>
       <c r="C294" s="10" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D294" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
@@ -16898,14 +16452,14 @@
       </c>
       <c r="H294" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>natação materiais</t>
+          <t>macacão neoprene</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
@@ -16914,14 +16468,14 @@
         </is>
       </c>
       <c r="C295" s="5" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D295" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E295" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
@@ -16936,14 +16490,14 @@
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="9" t="inlineStr">
         <is>
-          <t>roupa de natação infantil masculino</t>
+          <t>marcas de roupa de surf</t>
         </is>
       </c>
       <c r="B296" s="9" t="inlineStr">
@@ -16952,14 +16506,14 @@
         </is>
       </c>
       <c r="C296" s="10" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D296" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
@@ -16974,14 +16528,14 @@
       </c>
       <c r="H296" s="9" t="inlineStr">
         <is>
-          <t>negativa confirmada: linha adulta</t>
+          <t>pesquisa de marca/moda generica</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>acessórios natação</t>
+          <t>marcas de surfista</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
@@ -17012,14 +16566,14 @@
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>pesquisa de marca/moda generica</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="9" t="inlineStr">
         <is>
-          <t>artigos de natação</t>
+          <t>roupa de nadar</t>
         </is>
       </c>
       <c r="B298" s="9" t="inlineStr">
@@ -17035,7 +16589,7 @@
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
@@ -17050,14 +16604,14 @@
       </c>
       <c r="H298" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>artigos para natação</t>
+          <t>roupa mergulho neoprene</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
@@ -17088,14 +16642,14 @@
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="9" t="inlineStr">
         <is>
-          <t>calcao natacao</t>
+          <t>surf suit</t>
         </is>
       </c>
       <c r="B300" s="9" t="inlineStr">
@@ -17126,14 +16680,14 @@
       </c>
       <c r="H300" s="9" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>equipamentos para natacao</t>
+          <t>traje para natação</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
@@ -17149,7 +16703,7 @@
       </c>
       <c r="E301" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
@@ -17164,14 +16718,14 @@
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="9" t="inlineStr">
         <is>
-          <t>long surf</t>
+          <t>calção de natação masculino</t>
         </is>
       </c>
       <c r="B302" s="9" t="inlineStr">
@@ -17180,14 +16734,14 @@
         </is>
       </c>
       <c r="C302" s="10" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D302" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
@@ -17202,14 +16756,14 @@
       </c>
       <c r="H302" s="9" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>macacao para natacao</t>
+          <t>calção para natação</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
@@ -17218,14 +16772,14 @@
         </is>
       </c>
       <c r="C303" s="5" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D303" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E303" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Transactional</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
@@ -17240,14 +16794,14 @@
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="9" t="inlineStr">
         <is>
-          <t>macacão de natação masculino</t>
+          <t>loja roupa de surf</t>
         </is>
       </c>
       <c r="B304" s="9" t="inlineStr">
@@ -17256,14 +16810,14 @@
         </is>
       </c>
       <c r="C304" s="10" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D304" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
@@ -17278,14 +16832,14 @@
       </c>
       <c r="H304" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>intencao de loja fisica/generica</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>macacão neoprene</t>
+          <t>macacao surf feminino</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
@@ -17294,14 +16848,14 @@
         </is>
       </c>
       <c r="C305" s="5" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D305" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E305" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
@@ -17323,7 +16877,7 @@
     <row r="306">
       <c r="A306" s="9" t="inlineStr">
         <is>
-          <t>marcas de roupa de surf</t>
+          <t>macacão de surf feminino</t>
         </is>
       </c>
       <c r="B306" s="9" t="inlineStr">
@@ -17332,14 +16886,14 @@
         </is>
       </c>
       <c r="C306" s="10" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D306" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
@@ -17354,14 +16908,14 @@
       </c>
       <c r="H306" s="9" t="inlineStr">
         <is>
-          <t>pesquisa de marca/moda generica</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>marcas de surfista</t>
+          <t>roupa de borracha feminina</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
@@ -17370,7 +16924,7 @@
         </is>
       </c>
       <c r="C307" s="5" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D307" s="12" t="n">
         <v>0</v>
@@ -17392,14 +16946,14 @@
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
-          <t>pesquisa de marca/moda generica</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="9" t="inlineStr">
         <is>
-          <t>roupa de nadar</t>
+          <t>roupa para mergulho neoprene</t>
         </is>
       </c>
       <c r="B308" s="9" t="inlineStr">
@@ -17408,14 +16962,14 @@
         </is>
       </c>
       <c r="C308" s="10" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D308" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
@@ -17430,14 +16984,14 @@
       </c>
       <c r="H308" s="9" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>roupa mergulho neoprene</t>
+          <t>roupa para nadar</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -17446,14 +17000,14 @@
         </is>
       </c>
       <c r="C309" s="5" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D309" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E309" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
@@ -17468,14 +17022,14 @@
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="9" t="inlineStr">
         <is>
-          <t>surf suit</t>
+          <t>roupas de mergulho 5mm</t>
         </is>
       </c>
       <c r="B310" s="9" t="inlineStr">
@@ -17484,14 +17038,14 @@
         </is>
       </c>
       <c r="C310" s="10" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D310" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
@@ -17506,14 +17060,14 @@
       </c>
       <c r="H310" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>intencao mergulho: produto nao atende</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>traje para natação</t>
+          <t>surf long john</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
@@ -17522,14 +17076,14 @@
         </is>
       </c>
       <c r="C311" s="5" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D311" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E311" s="4" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
@@ -17544,14 +17098,14 @@
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
-          <t>peca de natacao que nao vendemos</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="9" t="inlineStr">
         <is>
-          <t>acessórios para natação</t>
+          <t>surf neoprene suit</t>
         </is>
       </c>
       <c r="B312" s="9" t="inlineStr">
@@ -17582,14 +17136,14 @@
       </c>
       <c r="H312" s="9" t="inlineStr">
         <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>calção de natação masculino</t>
+          <t>calça de natação</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -17598,19 +17152,19 @@
         </is>
       </c>
       <c r="C313" s="5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D313" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E313" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G313" s="4" t="inlineStr">
@@ -17627,7 +17181,7 @@
     <row r="314">
       <c r="A314" s="9" t="inlineStr">
         <is>
-          <t>calção para natação</t>
+          <t>calça para natação</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -17636,19 +17190,19 @@
         </is>
       </c>
       <c r="C314" s="10" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D314" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>Informational, Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G314" s="9" t="inlineStr">
@@ -17665,7 +17219,7 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>loja roupa de surf</t>
+          <t>loja de roupa de natação</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
@@ -17674,7 +17228,7 @@
         </is>
       </c>
       <c r="C315" s="5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D315" s="12" t="n">
         <v>0</v>
@@ -17686,7 +17240,7 @@
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G315" s="4" t="inlineStr">
@@ -17703,7 +17257,7 @@
     <row r="316">
       <c r="A316" s="9" t="inlineStr">
         <is>
-          <t>macacao surf feminino</t>
+          <t>macacao neoprene feminino</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -17712,19 +17266,19 @@
         </is>
       </c>
       <c r="C316" s="10" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D316" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G316" s="9" t="inlineStr">
@@ -17741,7 +17295,7 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>macacão de surf feminino</t>
+          <t>macacão neoprene feminino</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
@@ -17750,7 +17304,7 @@
         </is>
       </c>
       <c r="C317" s="5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D317" s="12" t="n">
         <v>0</v>
@@ -17762,7 +17316,7 @@
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G317" s="4" t="inlineStr">
@@ -17779,7 +17333,7 @@
     <row r="318">
       <c r="A318" s="9" t="inlineStr">
         <is>
-          <t>roupa de borracha feminina</t>
+          <t>material para natacao</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -17788,19 +17342,19 @@
         </is>
       </c>
       <c r="C318" s="10" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D318" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational, Commercial</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G318" s="9" t="inlineStr">
@@ -17810,14 +17364,14 @@
       </c>
       <c r="H318" s="9" t="inlineStr">
         <is>
-          <t>aderencia baixa ao produto</t>
+          <t>acessorios/equipamentos: fora do escopo</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>roupa de natação feminina infantil</t>
+          <t>melhores maios para natação</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -17826,19 +17380,19 @@
         </is>
       </c>
       <c r="C319" s="5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D319" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E319" s="4" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G319" s="4" t="inlineStr">
@@ -17848,14 +17402,14 @@
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
-          <t>negativa confirmada: linha adulta</t>
+          <t>peca de natacao que nao vendemos</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="9" t="inlineStr">
         <is>
-          <t>roupa para mergulho neoprene</t>
+          <t>moda surf masculina</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -17864,19 +17418,19 @@
         </is>
       </c>
       <c r="C320" s="10" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D320" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G320" s="9" t="inlineStr">
@@ -17886,14 +17440,14 @@
       </c>
       <c r="H320" s="9" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>pesquisa de marca/moda generica</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>roupa para nadar</t>
+          <t>natação masculina</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -17902,7 +17456,7 @@
         </is>
       </c>
       <c r="C321" s="5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D321" s="12" t="n">
         <v>0</v>
@@ -17914,7 +17468,7 @@
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G321" s="4" t="inlineStr">
@@ -17931,7 +17485,7 @@
     <row r="322">
       <c r="A322" s="9" t="inlineStr">
         <is>
-          <t>roupas de mergulho 5mm</t>
+          <t>roupa de surf john</t>
         </is>
       </c>
       <c r="B322" s="9" t="inlineStr">
@@ -17940,19 +17494,19 @@
         </is>
       </c>
       <c r="C322" s="10" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D322" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>Informational, Commercial</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G322" s="9" t="inlineStr">
@@ -17962,14 +17516,14 @@
       </c>
       <c r="H322" s="9" t="inlineStr">
         <is>
-          <t>intencao mergulho: produto nao atende</t>
+          <t>produto nao vendido (roupa fechada)</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>surf long john</t>
+          <t>roupa de natação masculina profissional</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
@@ -17978,19 +17532,15 @@
         </is>
       </c>
       <c r="C323" s="5" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="D323" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E323" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="E323" s="4" t="inlineStr"/>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G323" s="4" t="inlineStr">
@@ -18000,14 +17550,14 @@
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
+          <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
-          <t>surf neoprene suit</t>
+          <t>roupa para aula de natação masculino</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -18016,19 +17566,15 @@
         </is>
       </c>
       <c r="C324" s="10" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="D324" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E324" s="9" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E324" s="9" t="inlineStr"/>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="G324" s="9" t="inlineStr">
@@ -18038,498 +17584,12 @@
       </c>
       <c r="H324" s="9" t="inlineStr">
         <is>
-          <t>produto nao vendido (roupa fechada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="4" t="inlineStr">
-        <is>
-          <t>acessorios natacao</t>
-        </is>
-      </c>
-      <c r="B325" s="4" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C325" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D325" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E325" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F325" s="4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G325" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H325" s="4" t="inlineStr">
-        <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="9" t="inlineStr">
-        <is>
-          <t>calça de natação</t>
-        </is>
-      </c>
-      <c r="B326" s="9" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C326" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="D326" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E326" s="9" t="inlineStr">
-        <is>
-          <t>Informational, Commercial</t>
-        </is>
-      </c>
-      <c r="F326" s="9" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G326" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H326" s="9" t="inlineStr">
-        <is>
-          <t>peca de natacao que nao vendemos</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="4" t="inlineStr">
-        <is>
-          <t>calça para natação</t>
-        </is>
-      </c>
-      <c r="B327" s="4" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C327" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D327" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E327" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F327" s="4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G327" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H327" s="4" t="inlineStr">
-        <is>
-          <t>peca de natacao que nao vendemos</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="9" t="inlineStr">
-        <is>
-          <t>loja de roupa de natação</t>
-        </is>
-      </c>
-      <c r="B328" s="9" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C328" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="D328" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E328" s="9" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F328" s="9" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G328" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H328" s="9" t="inlineStr">
-        <is>
-          <t>intencao de loja fisica/generica</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="4" t="inlineStr">
-        <is>
-          <t>macacao neoprene feminino</t>
-        </is>
-      </c>
-      <c r="B329" s="4" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C329" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D329" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E329" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="F329" s="4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G329" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H329" s="4" t="inlineStr">
-        <is>
-          <t>produto nao vendido (roupa fechada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="9" t="inlineStr">
-        <is>
-          <t>macacão neoprene feminino</t>
-        </is>
-      </c>
-      <c r="B330" s="9" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C330" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="D330" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E330" s="9" t="inlineStr">
-        <is>
-          <t>Informational, Commercial</t>
-        </is>
-      </c>
-      <c r="F330" s="9" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G330" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H330" s="9" t="inlineStr">
-        <is>
-          <t>produto nao vendido (roupa fechada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="4" t="inlineStr">
-        <is>
-          <t>material para natacao</t>
-        </is>
-      </c>
-      <c r="B331" s="4" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C331" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D331" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E331" s="4" t="inlineStr">
-        <is>
-          <t>Informational, Commercial</t>
-        </is>
-      </c>
-      <c r="F331" s="4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G331" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H331" s="4" t="inlineStr">
-        <is>
-          <t>acessorios/equipamentos: fora do escopo</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="9" t="inlineStr">
-        <is>
-          <t>melhores maios para natação</t>
-        </is>
-      </c>
-      <c r="B332" s="9" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C332" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="D332" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E332" s="9" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F332" s="9" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G332" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H332" s="9" t="inlineStr">
-        <is>
-          <t>peca de natacao que nao vendemos</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="4" t="inlineStr">
-        <is>
-          <t>moda surf masculina</t>
-        </is>
-      </c>
-      <c r="B333" s="4" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C333" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D333" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E333" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F333" s="4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G333" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H333" s="4" t="inlineStr">
-        <is>
-          <t>pesquisa de marca/moda generica</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="9" t="inlineStr">
-        <is>
-          <t>natação masculina</t>
-        </is>
-      </c>
-      <c r="B334" s="9" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C334" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="D334" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E334" s="9" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="F334" s="9" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G334" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H334" s="9" t="inlineStr">
-        <is>
           <t>aderencia baixa ao produto</t>
         </is>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" s="4" t="inlineStr">
-        <is>
-          <t>roupa de surf john</t>
-        </is>
-      </c>
-      <c r="B335" s="4" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C335" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D335" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E335" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F335" s="4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G335" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H335" s="4" t="inlineStr">
-        <is>
-          <t>produto nao vendido (roupa fechada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="9" t="inlineStr">
-        <is>
-          <t>roupa de natação masculina profissional</t>
-        </is>
-      </c>
-      <c r="B336" s="9" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C336" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="D336" s="11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E336" s="9" t="inlineStr"/>
-      <c r="F336" s="9" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G336" s="9" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H336" s="9" t="inlineStr">
-        <is>
-          <t>aderencia baixa ao produto</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="4" t="inlineStr">
-        <is>
-          <t>roupa para aula de natação masculino</t>
-        </is>
-      </c>
-      <c r="B337" s="4" t="inlineStr">
-        <is>
-          <t>fora-da-campanha (observacao)</t>
-        </is>
-      </c>
-      <c r="C337" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D337" s="12" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E337" s="4" t="inlineStr"/>
-      <c r="F337" s="4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="G337" s="4" t="inlineStr">
-        <is>
-          <t>kw-manager</t>
-        </is>
-      </c>
-      <c r="H337" s="4" t="inlineStr">
-        <is>
-          <t>aderencia baixa ao produto</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H337"/>
+  <autoFilter ref="A1:H324"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
